--- a/SLR/Full-Paper-Read/Paper-Review/PS10.xlsx
+++ b/SLR/Full-Paper-Read/Paper-Review/PS10.xlsx
@@ -11,8 +11,24 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment authorId="0" ref="I4">
+      <text>
+        <t xml:space="preserve">A safety-critical CPS based control system with unmanned wireless sensors, such as unmanned substation (of an electric power corporation) in a smart grid.
+	-Adnan Ashraf</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="56">
   <si>
     <t>ID</t>
   </si>
@@ -26,40 +42,34 @@
     <t>The paper proposes the following contributions:</t>
   </si>
   <si>
-    <t>The paper motivates the need for elasticity in the process of integrating processes, people, and things. They identify the following aspects important for future integration, reusability, smart things, adatopn, human-based computing. The paper discuss if current practices are capable to capture these concerns. They argue that new emerging concerns need to be adressed in order to acheive elastic systems, but the paper mostly discusses a vision for this.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The paper frames elasticity in the framing of cyber-physical ecosystems, but mostly disucss the term elastic and its place in engineering. </t>
+    <t>This paper proposes a systematic virtual networking architecture to perform the global virtualization control and monitoring of a CPS, in which network functions virtualization (NFV) configu- ration and orchestration can be realized.</t>
+  </si>
+  <si>
+    <t>&lt;add your comment here if any&gt;</t>
   </si>
   <si>
     <t>CPS Case Study / Example availability</t>
   </si>
   <si>
-    <t>&lt;add your comment here if any&gt;</t>
-  </si>
-  <si>
     <t>SECO Tools Availability (add repository or website in the comment)</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
+    <t>architecture</t>
+  </si>
+  <si>
     <t>Related Challenge - See SPE paper (Write Others in comment cell)</t>
   </si>
   <si>
-    <t>Data</t>
-  </si>
-  <si>
-    <t>Intelligence and automation</t>
-  </si>
-  <si>
     <t>Others</t>
   </si>
   <si>
     <t>n.a.</t>
   </si>
   <si>
-    <t>People, heterogenity, buisness, re-usability, stakeholder engagement</t>
+    <t>systemc architecture + lifetime extension (there are two unresolved problems for a software- defined CPS. First, a feasible systemic architecture is a must for software-defined CPS, which should provide a global vir- tualization management and closed-loop control between the cyber side and the physical side in a CPS. Second, the life- time of a software-defined CPS scenario needs to be extended for critical applications. )</t>
   </si>
   <si>
     <t>Does it contribute to answer RQ1?</t>
@@ -68,9 +78,6 @@
     <t>Y</t>
   </si>
   <si>
-    <t>Yes, since the discussed topic is related to ecosystems. But, the paper is not mainly interested in the topic related to RQ1, but discusses it nontehteless</t>
-  </si>
-  <si>
     <t>Does the paper present methods, tools, and benefits in terms of industry/academia collaboration? If so, write what methods, tools, and benefits in the comment column</t>
   </si>
   <si>
@@ -80,16 +87,10 @@
     <t>Application Domain(s) (at least one or domain independent)</t>
   </si>
   <si>
-    <t>Digital Life</t>
-  </si>
-  <si>
-    <t>Cloud computing, IoT, IT, Human-based computing</t>
+    <t>Application Domain Independent</t>
   </si>
   <si>
     <t>Quality Evaluation (From 1 to 10) - From "Quality" Tab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This is an opinion paper, with quite low validity in my opinion, missing many parts of what would be expected for this kind of paper. </t>
   </si>
   <si>
     <t>RQ1: In the SECO, what are the main challenges faced during the CPS development?</t>
@@ -565,7 +566,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="58">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -584,7 +585,7 @@
     <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="8" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="9" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="10" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="11" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -604,7 +605,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf borderId="18" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="16" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf borderId="18" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
@@ -613,18 +617,21 @@
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
     <xf borderId="20" fillId="4" fontId="1" numFmtId="1" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="18" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
     <xf borderId="16" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="19" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="18" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
     <xf borderId="19" fillId="5" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf borderId="18" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
     <xf borderId="21" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
@@ -634,9 +641,6 @@
     <xf borderId="18" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="18" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
     <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
@@ -668,9 +672,6 @@
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="24" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="25" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
     <xf borderId="26" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -682,7 +683,7 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="24" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" textRotation="90"/>
@@ -691,7 +692,7 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="25" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -701,9 +702,6 @@
     </xf>
     <xf borderId="25" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="25" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="25" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -1025,7 +1023,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="17">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18"/>
@@ -1033,7 +1031,7 @@
       <c r="G4" s="18"/>
       <c r="H4" s="18"/>
       <c r="I4" s="19" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
@@ -1041,10 +1039,10 @@
         <v>3.0</v>
       </c>
       <c r="B5" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="20" t="s">
         <v>8</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>9</v>
       </c>
       <c r="D5" s="18"/>
       <c r="E5" s="18"/>
@@ -1052,7 +1050,7 @@
       <c r="G5" s="18"/>
       <c r="H5" s="18"/>
       <c r="I5" s="21" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -1065,23 +1063,23 @@
       <c r="C6" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="23" t="s">
         <v>13</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="22" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
@@ -1089,37 +1087,37 @@
         <v>5.0</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
+        <v>14</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
       <c r="H7" s="18"/>
-      <c r="I7" s="22" t="s">
-        <v>18</v>
+      <c r="I7" s="26" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="16">
         <v>6.0</v>
       </c>
-      <c r="B8" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24"/>
+      <c r="B8" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
       <c r="H8" s="18"/>
-      <c r="I8" s="27" t="s">
-        <v>7</v>
+      <c r="I8" s="26" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -1127,18 +1125,18 @@
         <v>7.0</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="24"/>
+        <v>17</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
       <c r="H9" s="18"/>
-      <c r="I9" s="21" t="s">
-        <v>7</v>
+      <c r="I9" s="30" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -1146,28 +1144,28 @@
         <v>8.0</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" s="22" t="s">
-        <v>23</v>
+        <v>18</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="26" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -1175,30 +1173,30 @@
         <v>9.0</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="31">
+        <v>20</v>
+      </c>
+      <c r="C11" s="33">
         <f>Quality!C29</f>
-        <v>4.074074074</v>
-      </c>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="24"/>
-      <c r="I11" s="32" t="s">
-        <v>25</v>
+        <v>10</v>
+      </c>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="30" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1"/>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="B14" s="33" t="s">
-        <v>26</v>
+      <c r="B14" s="34" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="B15" s="33" t="s">
-        <v>27</v>
+      <c r="B15" s="34" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1"/>
@@ -2238,7 +2236,8 @@
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -2257,82 +2256,82 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34"/>
-      <c r="B1" s="35" t="s">
+      <c r="A1" s="35"/>
+      <c r="B1" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="37"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="39"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="43"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="44"/>
+      <c r="B3" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="D3" s="37"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="43"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="44"/>
+      <c r="B4" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="C4" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="44"/>
+      <c r="B5" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="36"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="38"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="39" t="s">
+      <c r="C5" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="44"/>
+      <c r="B6" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="41">
-        <v>1.0</v>
-      </c>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="42"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="43"/>
-      <c r="B3" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="44">
-        <v>0.5</v>
-      </c>
-      <c r="D3" s="36"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="42"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="43"/>
-      <c r="B4" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="44">
-        <v>0.5</v>
-      </c>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="43"/>
-      <c r="B5" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="41">
-        <v>1.0</v>
-      </c>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="43"/>
-      <c r="B6" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="44">
-        <v>0.5</v>
-      </c>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
+      <c r="C6" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
     </row>
     <row r="7">
       <c r="A7" s="45"/>
-      <c r="B7" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="41">
+      <c r="B7" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="42">
         <v>1.0</v>
       </c>
       <c r="D7" s="46">
@@ -2341,139 +2340,139 @@
       </c>
       <c r="E7" s="46">
         <f>(SUM(C2:C7)/D7)*10</f>
-        <v>7.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="48" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="49">
+        <v>1.0</v>
+      </c>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="44"/>
+      <c r="B9" s="48" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="49">
+        <v>1.0</v>
+      </c>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="44"/>
+      <c r="B10" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="49">
+        <v>1.0</v>
+      </c>
+      <c r="D10" s="37"/>
+      <c r="E10" s="37"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="44"/>
+      <c r="B11" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="49">
+        <v>1.0</v>
+      </c>
+      <c r="D11" s="37"/>
+      <c r="E11" s="37"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="44"/>
+      <c r="B12" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="48" t="s">
+      <c r="C12" s="49">
+        <v>1.0</v>
+      </c>
+      <c r="D12" s="37"/>
+      <c r="E12" s="37"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="44"/>
+      <c r="B13" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="49">
-        <v>0.5</v>
-      </c>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="43"/>
-      <c r="B9" s="48" t="s">
+      <c r="C13" s="49">
+        <v>1.0</v>
+      </c>
+      <c r="D13" s="37"/>
+      <c r="E13" s="37"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="44"/>
+      <c r="B14" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="49">
-        <v>0.5</v>
-      </c>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="43"/>
-      <c r="B10" s="48" t="s">
+      <c r="C14" s="49">
+        <v>1.0</v>
+      </c>
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="44"/>
+      <c r="B15" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="49">
-        <v>0.5</v>
-      </c>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="43"/>
-      <c r="B11" s="48" t="s">
+      <c r="C15" s="49">
+        <v>1.0</v>
+      </c>
+      <c r="D15" s="37"/>
+      <c r="E15" s="37"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="44"/>
+      <c r="B16" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="49">
-        <v>0.0</v>
-      </c>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="43"/>
-      <c r="B12" s="48" t="s">
+      <c r="C16" s="49">
+        <v>1.0</v>
+      </c>
+      <c r="D16" s="37"/>
+      <c r="E16" s="37"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="44"/>
+      <c r="B17" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="49">
-        <v>0.0</v>
-      </c>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="43"/>
-      <c r="B13" s="48" t="s">
+      <c r="C17" s="49">
+        <v>1.0</v>
+      </c>
+      <c r="D17" s="37"/>
+      <c r="E17" s="37"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="44"/>
+      <c r="B18" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="49">
-        <v>0.0</v>
-      </c>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="43"/>
-      <c r="B14" s="48" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="49">
-        <v>0.5</v>
-      </c>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="43"/>
-      <c r="B15" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" s="49">
-        <v>0.5</v>
-      </c>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="43"/>
-      <c r="B16" s="48" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="49">
-        <v>0.0</v>
-      </c>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="43"/>
-      <c r="B17" s="48" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" s="49">
-        <v>0.5</v>
-      </c>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="43"/>
-      <c r="B18" s="48" t="s">
-        <v>48</v>
-      </c>
       <c r="C18" s="49">
-        <v>0.0</v>
-      </c>
-      <c r="D18" s="36"/>
-      <c r="E18" s="36"/>
+        <v>1.0</v>
+      </c>
+      <c r="D18" s="37"/>
+      <c r="E18" s="37"/>
     </row>
     <row r="19">
       <c r="A19" s="45"/>
       <c r="B19" s="48" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C19" s="49">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="D19" s="46">
         <f>COUNTIF(B8:B19,"&lt;&gt;text")</f>
@@ -2481,75 +2480,75 @@
       </c>
       <c r="E19" s="46">
         <f>(SUM(C8:C19)/D19)*10</f>
-        <v>2.916666667</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="50" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="51" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="44"/>
+      <c r="B21" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="44"/>
+      <c r="B22" s="51" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="44"/>
+      <c r="B23" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="43"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="44"/>
+      <c r="B24" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="B20" s="51" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="52">
-        <v>0.0</v>
-      </c>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="43"/>
-      <c r="B21" s="51" t="s">
-        <v>52</v>
-      </c>
-      <c r="C21" s="52">
-        <v>0.0</v>
-      </c>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="43"/>
-      <c r="B22" s="51" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="52">
-        <v>0.0</v>
-      </c>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="43"/>
-      <c r="B23" s="51" t="s">
-        <v>54</v>
-      </c>
-      <c r="C23" s="52">
-        <v>0.0</v>
-      </c>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="42"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="43"/>
-      <c r="B24" s="51" t="s">
-        <v>55</v>
-      </c>
       <c r="C24" s="52">
-        <v>0.5</v>
-      </c>
-      <c r="D24" s="37"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="42"/>
+        <v>1.0</v>
+      </c>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="43"/>
     </row>
     <row r="25">
       <c r="A25" s="45"/>
       <c r="B25" s="51" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C25" s="52">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="D25" s="53">
         <f>COUNTIF(B20:B25,"&lt;&gt;text")</f>
@@ -2557,43 +2556,43 @@
       </c>
       <c r="E25" s="53">
         <f>(SUM(C20:C25)/D25)*10</f>
-        <v>1.666666667</v>
-      </c>
-      <c r="F25" s="42"/>
+        <v>10</v>
+      </c>
+      <c r="F25" s="43"/>
     </row>
     <row r="26">
       <c r="A26" s="54" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B26" s="55" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C26" s="56">
-        <v>0.5</v>
-      </c>
-      <c r="D26" s="37"/>
-      <c r="E26" s="37"/>
-      <c r="F26" s="42"/>
+        <v>1.0</v>
+      </c>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="43"/>
     </row>
     <row r="27">
-      <c r="A27" s="43"/>
+      <c r="A27" s="44"/>
       <c r="B27" s="55" t="s">
-        <v>59</v>
-      </c>
-      <c r="C27" s="57">
-        <v>1.0</v>
-      </c>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="42"/>
+        <v>54</v>
+      </c>
+      <c r="C27" s="56">
+        <v>1.0</v>
+      </c>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="43"/>
     </row>
     <row r="28">
       <c r="A28" s="45"/>
       <c r="B28" s="55" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C28" s="56">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="D28" s="53">
         <f>COUNTIF(B26:B28,"&lt;&gt;text")</f>
@@ -2601,18 +2600,18 @@
       </c>
       <c r="E28" s="53">
         <f>(SUM(C26:C28)/D28)*10</f>
-        <v>6.666666667</v>
-      </c>
-      <c r="F28" s="42"/>
+        <v>10</v>
+      </c>
+      <c r="F28" s="43"/>
     </row>
     <row r="29">
-      <c r="B29" s="58">
+      <c r="B29" s="57">
         <f>COUNTIF(B2:B28,"&lt;&gt;text")</f>
         <v>27</v>
       </c>
-      <c r="C29" s="58">
+      <c r="C29" s="57">
         <f>(SUM(C2:C28)/B29)*10</f>
-        <v>4.074074074</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
